--- a/Single-Issue-Bonding-Capacity.xlsx
+++ b/Single-Issue-Bonding-Capacity.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5E2734-EE74-4B6B-B947-1C21CB7E556E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCA4864-8CD5-4817-ADA5-F6F7952247E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{FF680310-9A50-6B4A-AC90-F1931ACC690E}"/>
   </bookViews>
@@ -14,7 +14,7 @@
     <definedName name="BondDate">_xlfn.ANCHORARRAY('Bond Model'!$F$46)</definedName>
     <definedName name="BondIssuance">'Bond Model'!$D$7</definedName>
     <definedName name="BondType">_xlfn.ANCHORARRAY('Bond Model'!$F$42)</definedName>
-    <definedName name="fx.DebtSizeIssueλ">_xlfn.LAMBDA(_xlop.CFADS,_xlop.DSCR,_xlop.COUPON,_xlop.DBTRSVPCT,_xlop.DBTRSVRATE,_xlop.ParValueIncr,_xlop.MONTHS,_xlop.MATURITY,_xlop.LastPayoffDate,_xlop.Lo,_xlop.Hi,_xlop.Iter, _xlfn.LET( _xlpm.Help, TRIM(_xlfn.TEXTSPLIT( "DESCRIPTION:       →Sizes a new serial debt issuance to a coverage test¶" &amp; "                   →Par is an OUTPUT - the sum of the sized maturities¶" &amp; "SUGGESTED ROW IDS: →Debt opening balance / Interest / Principal repaid /¶" &amp; "                   →Debt closing balance / Debt service / Reserve credit /¶" &amp; "                   →Net debt service¶" &amp; "VERSION:           →W Phillips, Aug-11-2026¶" &amp; "PARAMETERS:→¶" &amp; "CFADS              →(Required) Cash available for debt service, per period¶" &amp; "DSCR               →(Required) Debt service coverage ratio, per period¶" &amp; "COUPON             →(Required) Coupon on the tranche MATURING in each period¶" &amp; "→ - a curve, not one rate on the balance. Flat is fine.¶" &amp; "DBTRSVPCT          →(Required) Reserve as a % of MAXIMUM ANNUAL debt service¶" &amp; "→ 25% is a 3-of-12-months reserve. The largest is used.¶" &amp; "DBTRSVRATE         →(Required) Earnings rate credited on the reserve¶" &amp; "ParValueIncr       →(Required) Par rounding increment. 1 = none. Never 0.¶" &amp; "MONTHS             →(Required) Months of interest per period, eg. 10,12,12¶" &amp; "MATURITY           →(Optional) Maturity date of each period's tranche¶" &amp; "LastPayoffDate     →(Optional) Last date a maturity may fall on. Periods¶" &amp; "→ after it are not sized; the reserve releases at the last live one.¶" &amp; "Lo, Hi, Iter       →Internal - the bisection solver's state¶" &amp; "→¶" &amp; "EXAMPLE:           →=fx.DebtSizeIssueλ(M59#,M60#,M61#,M62#,M63#,M64#,M65#,M58#,PayoffDate)", "→", "¶")), _xlpm.ErrMsgs, {"CFADS must be a dynamic array holding cash available for debt service in each period";"DSCR must be a dynamic array holding the debt service coverage ratio for each period";"COUPON must be a dynamic array holding the coupon on the tranche maturing in each period";"DBTRSVPCT must be a dynamic array holding the reserve percentage for each period";"DBTRSVRATE must be a dynamic array holding the reserve earnings rate for each period";"ParValueIncr must be a dynamic array of par increments, every one greater than zero. Use 1 for no rounding";"MONTHS must be a dynamic array holding the months of interest accruing in each period";"MATURITY must be a dynamic array of maturity dates, the same width as CFADS"}, _xlpm.CFADS, IF(COLUMNS(_xlpm.CFADS) &lt;= 1, #VALUE!, _xlpm.CFADS), _xlpm.DSCR, IF(COLUMNS(_xlpm.DSCR) &lt;= 1, #VALUE!, _xlpm.DSCR), _xlpm.COUPON, IF(COLUMNS(_xlpm.COUPON) &lt;= 1, #VALUE!, _xlpm.COUPON), _xlpm.DBTRSVPCT, IF(COLUMNS(_xlpm.DBTRSVPCT) &lt;= 1, #VALUE!, _xlpm.DBTRSVPCT), _xlpm.DBTRSVRATE, IF(COLUMNS(_xlpm.DBTRSVRATE) &lt;= 1, #VALUE!, _xlpm.DBTRSVRATE), _xlpm.ParValueIncr, IF(OR(COLUMNS(_xlpm.ParValueIncr) &lt;= 1, MIN(_xlpm.ParValueIncr) &lt;= 0), #VALUE!, _xlpm.ParValueIncr), _xlpm.MONTHS, IF(COLUMNS(_xlpm.MONTHS) &lt;= 1, #VALUE!, _xlpm.MONTHS), _xlpm.Mat, IF(_xlfn.ISOMITTED(_xlpm.MATURITY), --(_xlpm.CFADS &lt;= 0), IF(COLUMNS(_xlpm.MATURITY) &lt;&gt; COLUMNS(_xlpm.CFADS), #VALUE!, _xlpm.MATURITY)), _xlpm.Pay, IF(_xlfn.ISOMITTED(_xlpm.MATURITY), 0, IF(_xlfn.ISOMITTED(_xlpm.LastPayoffDate), MAX(_xlpm.Mat), _xlpm.LastPayoffDate)), _xlpm.Errors, _xlfn.VSTACK(OR(ISERROR(_xlpm.CFADS)), OR(ISERROR(_xlpm.DSCR)), OR(ISERROR(_xlpm.COUPON)), OR(ISERROR(_xlpm.DBTRSVPCT)), OR(ISERROR(_xlpm.DBTRSVRATE)), OR(ISERROR(_xlpm.ParValueIncr)), OR(ISERROR(_xlpm.MONTHS)), OR(ISERROR(_xlpm.Mat))), _xlpm.Messages, _xlfn._xlws.FILTER(_xlpm.ErrMsgs, _xlpm.Errors, ""), _xlpm.Periods, COLUMNS(_xlpm.CFADS), _xlpm.Idx, _xlfn.SEQUENCE(1, _xlpm.Periods), _xlpm.RsvPct, MAX(_xlpm.DBTRSVPCT), _xlpm.Live, --(_xlpm.Mat &lt;= _xlpm.Pay), _xlpm.LastLive, MAX(_xlpm.Live * _xlpm.Idx), _xlpm.Creditλ, _xlfn.LAMBDA(_xlpm.res, _xlpm.res * _xlpm.DBTRSVRATE * _xlpm.MONTHS / 12 * _xlpm.Live + _xlpm.res * (_xlpm.Idx = _xlpm.LastLive)), _xlpm.CoupRemλ, _xlfn.LAMBDA(_xlpm.tc,_xlpm.res, _xlfn.LET( _xlpm.Cr, _xlpm.Creditλ(_xlpm.res), _xlfn.SCAN(_xlpm.tc, _xlpm.Idx, _xlfn.LAMBDA(_xlpm.rem,_xlpm.y, _xlfn.LET( _xlpm.Target, INDEX(_xlpm.CFADS, 1, _xlpm.y) / INDEX(_xlpm.DSCR, 1, _xlpm.y) * INDEX(_xlpm.Live, 1, _xlpm.y), _xlpm.Intr, _xlpm.rem * INDEX(_xlpm.MONTHS, 1, _xlpm.y) / 12, _xlpm.Princ, FLOOR(MAX(0, _xlpm.Target - _xlpm.Intr + INDEX(_xlpm.Cr, 1, _xlpm.y)) * INDEX(_xlpm.Live, 1, _xlpm.y), INDEX(_xlpm.ParValueIncr, 1, _xlpm.y)), _xlpm.rem - _xlpm.Princ * INDEX(_xlpm.COUPON, 1, _xlpm.y) ))) )), _xlpm.Partsλ, _xlfn.LAMBDA(_xlpm.tc,_xlpm.res, _xlfn.LET( _xlpm.Aft, _xlpm.CoupRemλ(_xlpm.tc, _xlpm.res), _xlpm.Bef, _xlfn.HSTACK(_xlpm.tc, _xlfn.DROP(_xlpm.Aft, , -1)), _xlpm.Intr, _xlpm.Bef * _xlpm.MONTHS / 12, _xlpm.Raw, _xlpm.CFADS / _xlpm.DSCR * _xlpm.Live - _xlpm.Intr + _xlpm.Creditλ(_xlpm.res), _xlpm.Prin, FLOOR(IF(_xlpm.Raw &lt; 0, 0, _xlpm.Raw) * _xlpm.Live, _xlpm.ParValueIncr), _xlfn.VSTACK(_xlpm.Prin, _xlpm.Intr) )), _xlpm.Finalλ, _xlfn.LAMBDA(_xlpm.parts, _xlfn.LET( _xlpm.Prin, INDEX(_xlpm.parts, 1, 0), _xlpm.TrueTC, SUM(_xlpm.Prin * _xlpm.COUPON), _xlpm.Par, SUM(_xlpm.Prin), _xlpm.Cum, _xlfn.SCAN(0, _xlpm.Idx, _xlfn.LAMBDA(_xlpm.a,_xlpm.y, _xlpm.a + INDEX(_xlpm.Prin, 1, _xlpm.y))), _xlpm.ClEnd, _xlpm.Par - _xlpm.Cum, _xlpm.OpEnd, _xlfn.HSTACK(_xlpm.Par, _xlfn.DROP(_xlpm.ClEnd, , -1)), _xlpm.CumC, _xlfn.SCAN(0, _xlpm.Idx, _xlfn.LAMBDA(_xlpm.a,_xlpm.y, _xlpm.a + INDEX(_xlpm.Prin, 1, _xlpm.y) * INDEX(_xlpm.COUPON, 1, _xlpm.y))), _xlpm.RemBef, _xlpm.TrueTC - _xlfn.HSTACK(0, _xlfn.DROP(_xlpm.CumC, , -1)), _xlpm.IntEnd, _xlpm.RemBef * _xlpm.MONTHS / 12, _xlpm.RsvEnd, MAX(_xlpm.Prin + _xlpm.IntEnd) * _xlpm.RsvPct, _xlpm.CrEnd, _xlpm.Creditλ(_xlpm.RsvEnd), _xlfn.VSTACK(_xlpm.OpEnd, _xlpm.IntEnd, -_xlpm.Prin, _xlpm.ClEnd, _xlpm.Prin + _xlpm.IntEnd, -_xlpm.CrEnd, _xlpm.Prin + _xlpm.IntEnd - _xlpm.CrEnd) )), _xlpm.LoB, IF(_xlfn.ISOMITTED(_xlpm.Lo), 0, _xlpm.Lo), _xlpm.HiB, IF(_xlfn.ISOMITTED(_xlpm.Hi), SUM(_xlpm.CFADS * _xlpm.Live) / MIN(_xlpm.DSCR) * MAX(_xlpm.COUPON), _xlpm.Hi), _xlpm.Step, IF(_xlfn.ISOMITTED(_xlpm.Iter), -12, _xlpm.Iter), _xlpm.Mid, (_xlpm.LoB + _xlpm.HiB) / 2, _xlpm.Solveλ, _xlfn.LAMBDA(_xlpm.tc, _xlfn.LET(_xlpm.Rsv, _xlfn.REDUCE(0, _xlfn.SEQUENCE(1, 12), _xlfn.LAMBDA(_xlpm.r,_xlpm.ignore, _xlfn.LET(_xlpm.P, _xlpm.Partsλ(_xlpm.tc, _xlpm.r), MAX(INDEX(_xlpm.P, 1, 0) + INDEX(_xlpm.P, 2, 0)) * _xlpm.RsvPct))), _xlpm.Partsλ(_xlpm.tc, _xlpm.Rsv))), _xlpm.Grow, _xlpm.Step &lt; 0, _xlpm.Probe, IF(_xlpm.Grow, _xlpm.HiB, _xlpm.Mid), _xlpm.Parts, _xlpm.Solveλ(_xlpm.Probe), _xlpm.Residual, SUM(INDEX(_xlpm.Parts, 1, 0) * _xlpm.COUPON) - _xlpm.Probe, _xlpm.Up, _xlpm.Residual &gt;= 0, _xlpm.NxtLo, IF(_xlpm.Up, IF(_xlpm.Grow, _xlpm.LoB, _xlpm.Mid), _xlpm.LoB), _xlpm.NxtHi, IF(_xlpm.Up, IF(_xlpm.Grow, _xlpm.HiB * 2, _xlpm.HiB), IF(_xlpm.Grow, _xlpm.HiB, _xlpm.Mid)), _xlpm.NxtIt, IF(_xlpm.Up, _xlpm.Step + 1, IF(_xlpm.Grow, 1, _xlpm.Step + 1)), _xlpm.Result, IF(_xlpm.Step &gt;= 50, _xlpm.Finalλ(_xlpm.Solveλ(_xlpm.HiB)), fx.DebtSizeIssueλ(_xlpm.CFADS, _xlpm.DSCR, _xlpm.COUPON, _xlpm.DBTRSVPCT, _xlpm.DBTRSVRATE, _xlpm.ParValueIncr, _xlpm.MONTHS, _xlpm.Mat, _xlpm.Pay, _xlpm.NxtLo, _xlpm.NxtHi, _xlpm.NxtIt)), _xlpm.Return, IF(AND(_xlpm.Errors), 2, IF(OR(_xlpm.Errors), 3, IF(OR(ISERROR(_xlpm.Result)), 2, 1))), CHOOSE(_xlpm.Return, _xlpm.Result, _xlpm.Help, _xlpm.Messages) ) )</definedName>
+    <definedName name="fx.DebtSizeIssueλ">_xlfn.LAMBDA(_xlop.CFADS,_xlop.DSCR,_xlop.COUPON,_xlop.DBTRSVPCT,_xlop.DBTRSVRATE,_xlop.ParValueIncr,_xlop.MONTHS,_xlop.MATURITY,_xlop.LastPayoffDate,_xlop.Lo,_xlop.Hi,_xlop.Iter, _xlfn.LET( _xlpm.Help, TRIM(_xlfn.TEXTSPLIT( "FUNCTION:          →fx.DebtSizeIssueλ(CFADS, DSCR, COUPON, DBTRSVPCT,¶" &amp; "                   →DBTRSVRATE, ParValueIncr, MONTHS, [MATURITY],¶" &amp; "                   →[LastPayoffDate])¶" &amp; "DESCRIPTION:       →Sizes a new serial debt issuance to a coverage test¶" &amp; "                   →Par is an OUTPUT - the sum of the sized maturities¶" &amp; "WEBPAGE:           →github.com/wfphillips128/debt-size-issue-lambda¶" &amp; "SUGGESTED ROW IDS: →Debt opening balance / Interest / Principal repaid /¶" &amp; "                   →Debt closing balance / Debt service / Reserve credit /¶" &amp; "                   →Net debt service¶" &amp; "VERSION:           →W Phillips, Sep-05-2026¶" &amp; "PARAMETERS:→¶" &amp; "CFADS              →(Required) Cash available for debt service, per period¶" &amp; "DSCR               →(Required) Debt service coverage ratio, per period¶" &amp; "COUPON             →(Required) Coupon on the tranche MATURING in each period¶" &amp; "→ - a curve, not one rate on the balance. Flat is fine.¶" &amp; "DBTRSVPCT          →(Required) Reserve as a % of MAXIMUM ANNUAL debt service¶" &amp; "→ 25% is a 3-of-12-months reserve. The largest is used.¶" &amp; "DBTRSVRATE         →(Required) Earnings rate credited on the reserve¶" &amp; "ParValueIncr       →(Required) Par rounding increment. 1 = none. Never 0.¶" &amp; "MONTHS             →(Required) Months of interest per period, eg. 10,12,12¶" &amp; "MATURITY           →(Optional) Maturity date of each period's tranche¶" &amp; "LastPayoffDate     →(Optional) Last date a maturity may fall on. Periods¶" &amp; "→ after it are not sized; the reserve releases at the last live one.¶" &amp; "Lo, Hi, Iter       →Internal - the bisection solver's state¶" &amp; "→¶" &amp; "EXAMPLE:           →=fx.DebtSizeIssueλ(M59#,M60#,M61#,M62#,M63#,M64#,M65#,M58#,PayoffDate)", "→", "¶")), _xlpm.ErrMsgs, {"CFADS must be a dynamic array holding cash available for debt service in each period";"DSCR must be a dynamic array holding the debt service coverage ratio for each period";"COUPON must be a dynamic array holding the coupon on the tranche maturing in each period";"DBTRSVPCT must be a dynamic array holding the reserve percentage for each period";"DBTRSVRATE must be a dynamic array holding the reserve earnings rate for each period";"ParValueIncr must be a dynamic array of par increments, every one greater than zero. Use 1 for no rounding";"MONTHS must be a dynamic array holding the months of interest accruing in each period";"MATURITY must be a dynamic array of maturity dates, the same width as CFADS"}, _xlpm.CFADS, IF(COLUMNS(_xlpm.CFADS) &lt;= 1, #VALUE!, _xlpm.CFADS), _xlpm.DSCR, IF(COLUMNS(_xlpm.DSCR) &lt;= 1, #VALUE!, _xlpm.DSCR), _xlpm.COUPON, IF(COLUMNS(_xlpm.COUPON) &lt;= 1, #VALUE!, _xlpm.COUPON), _xlpm.DBTRSVPCT, IF(COLUMNS(_xlpm.DBTRSVPCT) &lt;= 1, #VALUE!, _xlpm.DBTRSVPCT), _xlpm.DBTRSVRATE, IF(COLUMNS(_xlpm.DBTRSVRATE) &lt;= 1, #VALUE!, _xlpm.DBTRSVRATE), _xlpm.ParValueIncr, IF(OR(COLUMNS(_xlpm.ParValueIncr) &lt;= 1, MIN(_xlpm.ParValueIncr) &lt;= 0), #VALUE!, _xlpm.ParValueIncr), _xlpm.MONTHS, IF(COLUMNS(_xlpm.MONTHS) &lt;= 1, #VALUE!, _xlpm.MONTHS), _xlpm.Mat, IF(_xlfn.ISOMITTED(_xlpm.MATURITY), --(_xlpm.CFADS &lt;= 0), IF(COLUMNS(_xlpm.MATURITY) &lt;&gt; COLUMNS(_xlpm.CFADS), #VALUE!, _xlpm.MATURITY)), _xlpm.Pay, IF(_xlfn.ISOMITTED(_xlpm.MATURITY), 0, IF(_xlfn.ISOMITTED(_xlpm.LastPayoffDate), MAX(_xlpm.Mat), _xlpm.LastPayoffDate)), _xlpm.Errors, _xlfn.VSTACK(OR(ISERROR(_xlpm.CFADS)), OR(ISERROR(_xlpm.DSCR)), OR(ISERROR(_xlpm.COUPON)), OR(ISERROR(_xlpm.DBTRSVPCT)), OR(ISERROR(_xlpm.DBTRSVRATE)), OR(ISERROR(_xlpm.ParValueIncr)), OR(ISERROR(_xlpm.MONTHS)), OR(ISERROR(_xlpm.Mat))), _xlpm.Messages, _xlfn._xlws.FILTER(_xlpm.ErrMsgs, _xlpm.Errors, ""), _xlpm.Periods, COLUMNS(_xlpm.CFADS), _xlpm.Idx, _xlfn.SEQUENCE(1, _xlpm.Periods), _xlpm.RsvPct, MAX(_xlpm.DBTRSVPCT), _xlpm.Live, --(_xlpm.Mat &lt;= _xlpm.Pay), _xlpm.LastLive, MAX(_xlpm.Live * _xlpm.Idx), _xlpm.Creditλ, _xlfn.LAMBDA(_xlpm.res, _xlpm.res * _xlpm.DBTRSVRATE * _xlpm.MONTHS / 12 * _xlpm.Live + _xlpm.res * (_xlpm.Idx = _xlpm.LastLive)), _xlpm.CoupRemλ, _xlfn.LAMBDA(_xlpm.tc,_xlpm.res, _xlfn.LET( _xlpm.Cr, _xlpm.Creditλ(_xlpm.res), _xlfn.SCAN(_xlpm.tc, _xlpm.Idx, _xlfn.LAMBDA(_xlpm.rem,_xlpm.y, _xlfn.LET( _xlpm.Target, INDEX(_xlpm.CFADS, 1, _xlpm.y) / INDEX(_xlpm.DSCR, 1, _xlpm.y) * INDEX(_xlpm.Live, 1, _xlpm.y), _xlpm.Intr, _xlpm.rem * INDEX(_xlpm.MONTHS, 1, _xlpm.y) / 12, _xlpm.Princ, FLOOR(MAX(0, _xlpm.Target - _xlpm.Intr + INDEX(_xlpm.Cr, 1, _xlpm.y)) * INDEX(_xlpm.Live, 1, _xlpm.y), INDEX(_xlpm.ParValueIncr, 1, _xlpm.y)), _xlpm.rem - _xlpm.Princ * INDEX(_xlpm.COUPON, 1, _xlpm.y) ))) )), _xlpm.Partsλ, _xlfn.LAMBDA(_xlpm.tc,_xlpm.res, _xlfn.LET( _xlpm.Aft, _xlpm.CoupRemλ(_xlpm.tc, _xlpm.res), _xlpm.Bef, _xlfn.HSTACK(_xlpm.tc, _xlfn.DROP(_xlpm.Aft, , -1)), _xlpm.Intr, _xlpm.Bef * _xlpm.MONTHS / 12, _xlpm.Raw, _xlpm.CFADS / _xlpm.DSCR * _xlpm.Live - _xlpm.Intr + _xlpm.Creditλ(_xlpm.res), _xlpm.Prin, FLOOR(IF(_xlpm.Raw &lt; 0, 0, _xlpm.Raw) * _xlpm.Live, _xlpm.ParValueIncr), _xlfn.VSTACK(_xlpm.Prin, _xlpm.Intr) )), _xlpm.Finalλ, _xlfn.LAMBDA(_xlpm.parts, _xlfn.LET( _xlpm.Prin, INDEX(_xlpm.parts, 1, 0), _xlpm.TrueTC, SUM(_xlpm.Prin * _xlpm.COUPON), _xlpm.Par, SUM(_xlpm.Prin), _xlpm.Cum, _xlfn.SCAN(0, _xlpm.Idx, _xlfn.LAMBDA(_xlpm.a,_xlpm.y, _xlpm.a + INDEX(_xlpm.Prin, 1, _xlpm.y))), _xlpm.ClEnd, _xlpm.Par - _xlpm.Cum, _xlpm.OpEnd, _xlfn.HSTACK(_xlpm.Par, _xlfn.DROP(_xlpm.ClEnd, , -1)), _xlpm.CumC, _xlfn.SCAN(0, _xlpm.Idx, _xlfn.LAMBDA(_xlpm.a,_xlpm.y, _xlpm.a + INDEX(_xlpm.Prin, 1, _xlpm.y) * INDEX(_xlpm.COUPON, 1, _xlpm.y))), _xlpm.RemBef, _xlpm.TrueTC - _xlfn.HSTACK(0, _xlfn.DROP(_xlpm.CumC, , -1)), _xlpm.IntEnd, _xlpm.RemBef * _xlpm.MONTHS / 12, _xlpm.RsvEnd, MAX(_xlpm.Prin + _xlpm.IntEnd) * _xlpm.RsvPct, _xlpm.CrEnd, _xlpm.Creditλ(_xlpm.RsvEnd), _xlfn.VSTACK(_xlpm.OpEnd, _xlpm.IntEnd, -_xlpm.Prin, _xlpm.ClEnd, _xlpm.Prin + _xlpm.IntEnd, -_xlpm.CrEnd, _xlpm.Prin + _xlpm.IntEnd - _xlpm.CrEnd) )), _xlpm.LoB, IF(_xlfn.ISOMITTED(_xlpm.Lo), 0, _xlpm.Lo), _xlpm.HiB, IF(_xlfn.ISOMITTED(_xlpm.Hi), SUM(_xlpm.CFADS * _xlpm.Live) / MIN(_xlpm.DSCR) * MAX(_xlpm.COUPON), _xlpm.Hi), _xlpm.Step, IF(_xlfn.ISOMITTED(_xlpm.Iter), -12, _xlpm.Iter), _xlpm.Mid, (_xlpm.LoB + _xlpm.HiB) / 2, _xlpm.Solveλ, _xlfn.LAMBDA(_xlpm.tc, _xlfn.LET(_xlpm.Rsv, _xlfn.REDUCE(0, _xlfn.SEQUENCE(1, 12), _xlfn.LAMBDA(_xlpm.r,_xlpm.ignore, _xlfn.LET(_xlpm.P, _xlpm.Partsλ(_xlpm.tc, _xlpm.r), MAX(INDEX(_xlpm.P, 1, 0) + INDEX(_xlpm.P, 2, 0)) * _xlpm.RsvPct))), _xlpm.Partsλ(_xlpm.tc, _xlpm.Rsv))), _xlpm.Grow, _xlpm.Step &lt; 0, _xlpm.Probe, IF(_xlpm.Grow, _xlpm.HiB, _xlpm.Mid), _xlpm.Parts, _xlpm.Solveλ(_xlpm.Probe), _xlpm.Residual, SUM(INDEX(_xlpm.Parts, 1, 0) * _xlpm.COUPON) - _xlpm.Probe, _xlpm.Up, _xlpm.Residual &gt;= 0, _xlpm.NxtLo, IF(_xlpm.Up, IF(_xlpm.Grow, _xlpm.LoB, _xlpm.Mid), _xlpm.LoB), _xlpm.NxtHi, IF(_xlpm.Up, IF(_xlpm.Grow, _xlpm.HiB * 2, _xlpm.HiB), IF(_xlpm.Grow, _xlpm.HiB, _xlpm.Mid)), _xlpm.NxtIt, IF(_xlpm.Up, _xlpm.Step + 1, IF(_xlpm.Grow, 1, _xlpm.Step + 1)), _xlpm.Result, IF(_xlpm.Step &gt;= 50, _xlpm.Finalλ(_xlpm.Solveλ(_xlpm.HiB)), fx.DebtSizeIssueλ(_xlpm.CFADS, _xlpm.DSCR, _xlpm.COUPON, _xlpm.DBTRSVPCT, _xlpm.DBTRSVRATE, _xlpm.ParValueIncr, _xlpm.MONTHS, _xlpm.Mat, _xlpm.Pay, _xlpm.NxtLo, _xlpm.NxtHi, _xlpm.NxtIt)), _xlpm.Return, IF(AND(_xlpm.Errors), 2, IF(OR(_xlpm.Errors), 3, IF(OR(ISERROR(_xlpm.Result)), 2, 1))), _xlpm.Output, CHOOSE(_xlpm.Return, _xlpm.Result, _xlpm.Help, _xlpm.Messages), _xlpm.Output ) )</definedName>
     <definedName name="LastPayoffDate">'Bond Model'!$C$34</definedName>
     <definedName name="MaxDeliveryDate">'Bond Model'!$C$32</definedName>
     <definedName name="MaxPayoffDate">'Bond Model'!$C$33</definedName>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -4293,7 +4293,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="65" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B65" s="66">
         <v>46600</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B66" s="66">
         <v>46631</v>
       </c>
@@ -4356,7 +4356,7 @@
       <c r="I66" s="25"/>
       <c r="K66" s="88"/>
     </row>
-    <row r="67" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B67" s="66">
         <v>46661</v>
       </c>
@@ -4376,7 +4376,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B68" s="66">
         <v>46692</v>
       </c>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W68" s="111"/>
     </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B69" s="66">
         <v>46722</v>
       </c>
@@ -4471,8 +4471,10 @@
         <f>SUM(M69:U69)</f>
         <v>1381125</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="AA69"/>
+      <c r="AB69"/>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B70" s="66">
         <v>46753</v>
       </c>
@@ -4523,8 +4525,10 @@
         <f>SUM(M70:U70)</f>
         <v>-6645000</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="AA70"/>
+      <c r="AB70"/>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B71" s="66">
         <v>46784</v>
       </c>
@@ -4569,8 +4573,10 @@
         <v>0</v>
       </c>
       <c r="Y71" s="111"/>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="AA71"/>
+      <c r="AB71"/>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B72" s="66">
         <v>46813</v>
       </c>
@@ -4618,8 +4624,10 @@
         <f>SUM(M72:U72)</f>
         <v>8026125</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="AA72"/>
+      <c r="AB72"/>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B73" s="66">
         <v>46844</v>
       </c>
@@ -4667,8 +4675,10 @@
         <f>SUM(M73:U73)</f>
         <v>-414741.25</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AA73"/>
+      <c r="AB73"/>
+    </row>
+    <row r="74" spans="2:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B74" s="66">
         <v>46874</v>
       </c>
@@ -4716,8 +4726,10 @@
         <f>SUM(M74:U74)</f>
         <v>7611383.75</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="AA74"/>
+      <c r="AB74"/>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B75" s="66">
         <v>46905</v>
       </c>
@@ -4732,7 +4744,7 @@
       </c>
       <c r="H75" s="55"/>
     </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B76" s="66">
         <v>46935</v>
       </c>
@@ -4756,7 +4768,7 @@
       <c r="T76"/>
       <c r="U76"/>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B77" s="66">
         <v>46966</v>
       </c>
@@ -4784,7 +4796,7 @@
       <c r="V77"/>
       <c r="W77"/>
     </row>
-    <row r="78" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B78" s="66">
         <v>46997</v>
       </c>
@@ -4812,7 +4824,7 @@
       <c r="V78"/>
       <c r="W78"/>
     </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B79" s="66">
         <v>47027</v>
       </c>
@@ -4840,7 +4852,7 @@
       <c r="V79"/>
       <c r="W79"/>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.35">
       <c r="B80" s="66">
         <v>47058</v>
       </c>
@@ -4855,11 +4867,11 @@
       </c>
       <c r="H80" s="55"/>
       <c r="K80" s="130" t="str" cm="1">
-        <f t="array" ref="K80:L101">fx.DebtSizeIssueλ()</f>
-        <v>DESCRIPTION:</v>
+        <f t="array" ref="K80:L105">fx.DebtSizeIssueλ()</f>
+        <v>FUNCTION:</v>
       </c>
       <c r="L80" t="str">
-        <v>Sizes a new serial debt issuance to a coverage test</v>
+        <v>fx.DebtSizeIssueλ(CFADS, DSCR, COUPON, DBTRSVPCT,</v>
       </c>
       <c r="M80"/>
       <c r="N80"/>
@@ -4891,7 +4903,7 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Par is an OUTPUT - the sum of the sized maturities</v>
+        <v>DBTRSVRATE, ParValueIncr, MONTHS, [MATURITY],</v>
       </c>
       <c r="M81"/>
       <c r="N81"/>
@@ -4920,10 +4932,10 @@
       </c>
       <c r="H82" s="55"/>
       <c r="K82" s="130" t="str">
-        <v>SUGGESTED ROW IDS:</v>
+        <v/>
       </c>
       <c r="L82" t="str">
-        <v>Debt opening balance / Interest / Principal repaid /</v>
+        <v>[LastPayoffDate])</v>
       </c>
       <c r="M82"/>
       <c r="N82"/>
@@ -4952,10 +4964,10 @@
       </c>
       <c r="H83" s="55"/>
       <c r="K83" s="130" t="str">
-        <v/>
+        <v>DESCRIPTION:</v>
       </c>
       <c r="L83" t="str">
-        <v>Debt closing balance / Debt service / Reserve credit /</v>
+        <v>Sizes a new serial debt issuance to a coverage test</v>
       </c>
       <c r="V83"/>
       <c r="W83"/>
@@ -4978,7 +4990,7 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Net debt service</v>
+        <v>Par is an OUTPUT - the sum of the sized maturities</v>
       </c>
       <c r="M84"/>
       <c r="N84"/>
@@ -5007,10 +5019,10 @@
       </c>
       <c r="H85" s="55"/>
       <c r="K85" t="str">
-        <v>VERSION:</v>
+        <v>WEBPAGE:</v>
       </c>
       <c r="L85" t="str">
-        <v>W Phillips, Aug-11-2026</v>
+        <v>github.com/wfphillips128/debt-size-issue-lambda</v>
       </c>
       <c r="M85"/>
       <c r="N85"/>
@@ -5039,10 +5051,10 @@
       </c>
       <c r="H86" s="55"/>
       <c r="K86" t="str">
-        <v>PARAMETERS:</v>
+        <v>SUGGESTED ROW IDS:</v>
       </c>
       <c r="L86" t="str">
-        <v/>
+        <v>Debt opening balance / Interest / Principal repaid /</v>
       </c>
       <c r="M86"/>
       <c r="N86"/>
@@ -5071,10 +5083,10 @@
       </c>
       <c r="H87" s="55"/>
       <c r="K87" t="str">
-        <v>CFADS</v>
+        <v/>
       </c>
       <c r="L87" t="str">
-        <v>(Required) Cash available for debt service, per period</v>
+        <v>Debt closing balance / Debt service / Reserve credit /</v>
       </c>
       <c r="M87"/>
       <c r="N87"/>
@@ -5103,10 +5115,10 @@
       </c>
       <c r="H88" s="55"/>
       <c r="K88" t="str">
-        <v>DSCR</v>
+        <v/>
       </c>
       <c r="L88" t="str">
-        <v>(Required) Debt service coverage ratio, per period</v>
+        <v>Net debt service</v>
       </c>
       <c r="M88"/>
       <c r="N88"/>
@@ -5135,10 +5147,10 @@
       </c>
       <c r="H89" s="55"/>
       <c r="K89" t="str">
-        <v>COUPON</v>
+        <v>VERSION:</v>
       </c>
       <c r="L89" t="str">
-        <v>(Required) Coupon on the tranche MATURING in each period</v>
+        <v>W Phillips, Sep-05-2026</v>
       </c>
       <c r="M89"/>
       <c r="N89"/>
@@ -5167,10 +5179,10 @@
       </c>
       <c r="H90" s="55"/>
       <c r="K90" t="str">
+        <v>PARAMETERS:</v>
+      </c>
+      <c r="L90" t="str">
         <v/>
-      </c>
-      <c r="L90" t="str">
-        <v>- a curve, not one rate on the balance. Flat is fine.</v>
       </c>
       <c r="M90"/>
       <c r="N90"/>
@@ -5199,10 +5211,10 @@
       </c>
       <c r="H91" s="55"/>
       <c r="K91" t="str">
-        <v>DBTRSVPCT</v>
+        <v>CFADS</v>
       </c>
       <c r="L91" t="str">
-        <v>(Required) Reserve as a % of MAXIMUM ANNUAL debt service</v>
+        <v>(Required) Cash available for debt service, per period</v>
       </c>
       <c r="M91"/>
       <c r="N91"/>
@@ -5231,10 +5243,10 @@
       </c>
       <c r="H92" s="55"/>
       <c r="K92" t="str">
-        <v/>
+        <v>DSCR</v>
       </c>
       <c r="L92" t="str">
-        <v>25% is a 3-of-12-months reserve. The largest is used.</v>
+        <v>(Required) Debt service coverage ratio, per period</v>
       </c>
       <c r="M92"/>
       <c r="N92"/>
@@ -5263,10 +5275,10 @@
       </c>
       <c r="H93" s="55"/>
       <c r="K93" t="str">
-        <v>DBTRSVRATE</v>
+        <v>COUPON</v>
       </c>
       <c r="L93" t="str">
-        <v>(Required) Earnings rate credited on the reserve</v>
+        <v>(Required) Coupon on the tranche MATURING in each period</v>
       </c>
       <c r="M93"/>
       <c r="N93"/>
@@ -5295,10 +5307,10 @@
       </c>
       <c r="H94" s="55"/>
       <c r="K94" t="str">
-        <v>ParValueIncr</v>
+        <v/>
       </c>
       <c r="L94" t="str">
-        <v>(Required) Par rounding increment. 1 = none. Never 0.</v>
+        <v>- a curve, not one rate on the balance. Flat is fine.</v>
       </c>
       <c r="M94"/>
       <c r="N94"/>
@@ -5327,10 +5339,10 @@
       </c>
       <c r="H95" s="55"/>
       <c r="K95" t="str">
-        <v>MONTHS</v>
+        <v>DBTRSVPCT</v>
       </c>
       <c r="L95" t="str">
-        <v>(Required) Months of interest per period, eg. 10,12,12</v>
+        <v>(Required) Reserve as a % of MAXIMUM ANNUAL debt service</v>
       </c>
       <c r="M95"/>
       <c r="N95"/>
@@ -5359,10 +5371,10 @@
       </c>
       <c r="H96" s="55"/>
       <c r="K96" t="str">
-        <v>MATURITY</v>
+        <v/>
       </c>
       <c r="L96" t="str">
-        <v>(Optional) Maturity date of each period's tranche</v>
+        <v>25% is a 3-of-12-months reserve. The largest is used.</v>
       </c>
       <c r="M96"/>
       <c r="N96"/>
@@ -5391,10 +5403,10 @@
       </c>
       <c r="H97" s="55"/>
       <c r="K97" t="str">
-        <v>LastPayoffDate</v>
+        <v>DBTRSVRATE</v>
       </c>
       <c r="L97" t="str">
-        <v>(Optional) Last date a maturity may fall on. Periods</v>
+        <v>(Required) Earnings rate credited on the reserve</v>
       </c>
       <c r="M97"/>
       <c r="N97"/>
@@ -5423,10 +5435,10 @@
       </c>
       <c r="H98" s="55"/>
       <c r="K98" t="str">
-        <v/>
+        <v>ParValueIncr</v>
       </c>
       <c r="L98" t="str">
-        <v>after it are not sized; the reserve releases at the last live one.</v>
+        <v>(Required) Par rounding increment. 1 = none. Never 0.</v>
       </c>
       <c r="M98"/>
       <c r="N98"/>
@@ -5455,10 +5467,10 @@
       </c>
       <c r="H99" s="55"/>
       <c r="K99" t="str">
-        <v>Lo, Hi, Iter</v>
+        <v>MONTHS</v>
       </c>
       <c r="L99" t="str">
-        <v>Internal - the bisection solver's state</v>
+        <v>(Required) Months of interest per period, eg. 10,12,12</v>
       </c>
       <c r="M99"/>
       <c r="N99"/>
@@ -5488,10 +5500,10 @@
       <c r="H100" s="55"/>
       <c r="J100"/>
       <c r="K100" t="str">
-        <v/>
+        <v>MATURITY</v>
       </c>
       <c r="L100" t="str">
-        <v/>
+        <v>(Optional) Maturity date of each period's tranche</v>
       </c>
       <c r="M100"/>
       <c r="N100"/>
@@ -5521,10 +5533,10 @@
       <c r="H101" s="55"/>
       <c r="J101"/>
       <c r="K101" t="str">
-        <v>EXAMPLE:</v>
+        <v>LastPayoffDate</v>
       </c>
       <c r="L101" t="str">
-        <v>=fx.DebtSizeIssueλ(M59#,M60#,M61#,M62#,M63#,M64#,M65#,M58#,PayoffDate)</v>
+        <v>(Optional) Last date a maturity may fall on. Periods</v>
       </c>
       <c r="M101"/>
       <c r="N101"/>
@@ -5553,8 +5565,12 @@
       </c>
       <c r="H102" s="55"/>
       <c r="J102"/>
-      <c r="K102"/>
-      <c r="L102"/>
+      <c r="K102" t="str">
+        <v/>
+      </c>
+      <c r="L102" t="str">
+        <v>after it are not sized; the reserve releases at the last live one.</v>
+      </c>
       <c r="M102"/>
       <c r="N102"/>
       <c r="O102"/>
@@ -5582,8 +5598,12 @@
       </c>
       <c r="H103" s="55"/>
       <c r="J103"/>
-      <c r="K103"/>
-      <c r="L103"/>
+      <c r="K103" t="str">
+        <v>Lo, Hi, Iter</v>
+      </c>
+      <c r="L103" t="str">
+        <v>Internal - the bisection solver's state</v>
+      </c>
       <c r="M103"/>
       <c r="N103"/>
       <c r="O103"/>
@@ -5611,8 +5631,12 @@
       </c>
       <c r="H104" s="55"/>
       <c r="J104"/>
-      <c r="K104"/>
-      <c r="L104"/>
+      <c r="K104" t="str">
+        <v/>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
       <c r="M104"/>
       <c r="N104"/>
       <c r="O104"/>
@@ -5640,8 +5664,12 @@
       </c>
       <c r="H105" s="55"/>
       <c r="J105"/>
-      <c r="K105"/>
-      <c r="L105"/>
+      <c r="K105" t="str">
+        <v>EXAMPLE:</v>
+      </c>
+      <c r="L105" t="str">
+        <v>=fx.DebtSizeIssueλ(M59#,M60#,M61#,M62#,M63#,M64#,M65#,M58#,PayoffDate)</v>
+      </c>
       <c r="M105"/>
       <c r="N105"/>
       <c r="O105"/>
